--- a/output/topology_excel/9238.xlsx
+++ b/output/topology_excel/9238.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -487,7 +487,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
         <v>13</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
         <v>13</v>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
         <v>13</v>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
         <v>13</v>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
         <v>13</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,54 +850,54 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
@@ -905,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>346</v>
+        <v>433</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -1015,7 +1015,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>433</v>
+        <v>136</v>
       </c>
       <c r="F27" t="n">
         <v>13</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>333</v>
+        <v>425</v>
       </c>
       <c r="F28" t="n">
-        <v>316</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B29" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>193</v>
+        <v>68</v>
       </c>
       <c r="F29" t="n">
-        <v>164</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F30" t="n">
         <v>13</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B31" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B32" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>108</v>
+        <v>235</v>
       </c>
       <c r="F32" t="n">
         <v>13</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B33" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>317</v>
       </c>
       <c r="F33" t="n">
         <v>13</v>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>103</v>
+        <v>235</v>
       </c>
       <c r="F34" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>201</v>
+        <v>320</v>
       </c>
       <c r="F35" t="n">
         <v>13</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>425</v>
+        <v>138</v>
       </c>
       <c r="F36" t="n">
         <v>13</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="F37" t="n">
         <v>13</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>330</v>
+        <v>181</v>
       </c>
       <c r="F38" t="n">
-        <v>316</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="F39" t="n">
         <v>13</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="F40" t="n">
-        <v>162</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F41" t="n">
         <v>13</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B42" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="F42" t="n">
         <v>13</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B43" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F43" t="n">
         <v>13</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>306</v>
+        <v>136</v>
       </c>
       <c r="F44" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B45" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="F45" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B46" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F46" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B47" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="F47" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B48" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>317</v>
+        <v>107</v>
       </c>
       <c r="F48" t="n">
         <v>13</v>
@@ -1499,7 +1499,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>320</v>
+        <v>186</v>
       </c>
       <c r="F49" t="n">
         <v>13</v>
@@ -1521,7 +1521,7 @@
         <v>10</v>
       </c>
       <c r="B50" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="F50" t="n">
         <v>13</v>
@@ -1543,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="B51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="F51" t="n">
         <v>13</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F52" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -1587,7 +1587,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="F54" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,18 +1642,18 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F55" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F56" t="n">
         <v>13</v>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F57" t="n">
         <v>13</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="F59" t="n">
         <v>13</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B60" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="F60" t="n">
         <v>13</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1774,18 +1774,18 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="F61" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B62" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,18 +1796,18 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>214</v>
+        <v>306</v>
       </c>
       <c r="F62" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B63" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,19 +1818,19 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F63" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B64" t="n">
         <v>17</v>
       </c>
-      <c r="B64" t="n">
-        <v>21</v>
-      </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1840,18 +1840,18 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="F64" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B65" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F65" t="n">
         <v>13</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>186</v>
+        <v>313</v>
       </c>
       <c r="F66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
@@ -1895,21 +1895,241 @@
         <v>19</v>
       </c>
       <c r="B67" t="n">
+        <v>24</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>301</v>
+      </c>
+      <c r="F67" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>19</v>
+      </c>
+      <c r="B68" t="n">
         <v>23</v>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>182</v>
-      </c>
-      <c r="F67" t="n">
-        <v>13</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>346</v>
+      </c>
+      <c r="F68" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>20</v>
+      </c>
+      <c r="B69" t="n">
+        <v>25</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>301</v>
+      </c>
+      <c r="F69" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>20</v>
+      </c>
+      <c r="B70" t="n">
+        <v>23</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>350</v>
+      </c>
+      <c r="F70" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>23</v>
+      </c>
+      <c r="B71" t="n">
+        <v>24</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>103</v>
+      </c>
+      <c r="F71" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>23</v>
+      </c>
+      <c r="B72" t="n">
+        <v>26</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>214</v>
+      </c>
+      <c r="F72" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>23</v>
+      </c>
+      <c r="B73" t="n">
+        <v>27</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>216</v>
+      </c>
+      <c r="F73" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>354</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2</v>
+      </c>
+      <c r="B75" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>344</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="n">
+        <v>15</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>183</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3</v>
+      </c>
+      <c r="B77" t="n">
+        <v>16</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>185</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9238.xlsx
+++ b/output/topology_excel/9238.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
